--- a/英语群_20260822.xlsx
+++ b/英语群_20260822.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\huil\checkin\WeChatTextExport\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\huil\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17175"/>
+    <workbookView windowHeight="17200"/>
   </bookViews>
   <sheets>
     <sheet name="最终版" sheetId="1" r:id="rId1"/>
@@ -1254,11 +1254,11 @@
       <c r="A1" s="24"/>
       <c r="B1" s="24">
         <f>SUM(B3:B1001)</f>
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C1" s="24">
         <f>SUM(C3:C1001)</f>
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D1" s="24">
         <f>SUM(D3:D1001)</f>
@@ -3086,11 +3086,11 @@
       </c>
       <c r="B45" s="3">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C45" s="3">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D45" s="3">
         <f t="shared" si="2"/>
@@ -3101,7 +3101,7 @@
         <v>7</v>
       </c>
       <c r="F45" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G45" s="5">
         <v>0</v>
